--- a/0_COLLECT_ZIVE_DATA/DUOM_2023/records_summary.xlsx
+++ b/0_COLLECT_ZIVE_DATA/DUOM_2023/records_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_COLLECT_ZIVE_DATA\DUOM_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7470FB30-A857-414E-846B-65CF0416CD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FACFD4F-29B7-4D4F-94D0-4FEA7F2E4018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1140" windowWidth="19200" windowHeight="7710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="149">
   <si>
     <t>nr</t>
+  </si>
+  <si>
+    <t>FOR_EXTERNAL_ANNOTATING</t>
+  </si>
+  <si>
+    <t>NOISES_ANNOTATED</t>
   </si>
   <si>
     <t>file_name</t>
@@ -829,29 +835,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -903,16 +911,16 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
@@ -920,1833 +928,1833 @@
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>128000</v>
       </c>
-      <c r="G2" s="2">
+      <c r="I2" s="2">
         <v>640</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>720</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>718</v>
       </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>2</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2" s="3">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3">
         <v>0.234375</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
       <c r="D3" t="s">
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
         <v>128000</v>
       </c>
-      <c r="G3" s="2">
+      <c r="I3" s="2">
         <v>640</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>739</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>737</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" s="3">
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3">
         <v>0.46875</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
       <c r="D4" t="s">
         <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="F4">
-        <v>127999</v>
-      </c>
-      <c r="G4" s="2">
-        <v>639.995</v>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
       </c>
       <c r="H4">
+        <v>127999</v>
+      </c>
+      <c r="I4" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J4">
         <v>612</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>610</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>2</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
       <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
         <v>6</v>
       </c>
-      <c r="N4" s="3">
+      <c r="P4" s="3">
         <v>6.562551269931796</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
       <c r="D5" t="s">
         <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="F5">
-        <v>127999</v>
-      </c>
-      <c r="G5" s="2">
-        <v>639.995</v>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
       </c>
       <c r="H5">
+        <v>127999</v>
+      </c>
+      <c r="I5" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J5">
         <v>564</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>559</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>5</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3">
         <v>7.8125610356330907E-2</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
       <c r="D6" t="s">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>127999</v>
-      </c>
-      <c r="G6" s="2">
-        <v>639.995</v>
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
       </c>
       <c r="H6">
+        <v>127999</v>
+      </c>
+      <c r="I6" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J6">
         <v>542</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>540</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3">
         <v>0.31250244142532357</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
       <c r="D7" t="s">
         <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="F7">
-        <v>127999</v>
-      </c>
-      <c r="G7" s="2">
-        <v>639.995</v>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
       </c>
       <c r="H7">
+        <v>127999</v>
+      </c>
+      <c r="I7" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J7">
         <v>581</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>580</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3">
         <v>0.31250244142532357</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
       <c r="D8" t="s">
         <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>43</v>
       </c>
-      <c r="F8">
-        <v>127999</v>
-      </c>
-      <c r="G8" s="2">
-        <v>639.995</v>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
       </c>
       <c r="H8">
+        <v>127999</v>
+      </c>
+      <c r="I8" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J8">
         <v>612</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>612</v>
       </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
         <v>2</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>0.93750732427597094</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
       <c r="D9" t="s">
         <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>47</v>
       </c>
-      <c r="F9">
-        <v>127999</v>
-      </c>
-      <c r="G9" s="2">
-        <v>639.995</v>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
       </c>
       <c r="H9">
+        <v>127999</v>
+      </c>
+      <c r="I9" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J9">
         <v>747</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>724</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>2</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>21</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9" s="3">
         <v>7.8125610356330907E-2</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
       <c r="D10" t="s">
         <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10">
-        <v>127999</v>
-      </c>
-      <c r="G10" s="2">
-        <v>639.995</v>
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
       </c>
       <c r="H10">
+        <v>127999</v>
+      </c>
+      <c r="I10" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J10">
         <v>717</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>708</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>4</v>
-      </c>
-      <c r="K10">
-        <v>5</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>6.0937976077938112</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
       <c r="D11" t="s">
         <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
       </c>
-      <c r="F11">
-        <v>127999</v>
-      </c>
-      <c r="G11" s="2">
-        <v>639.995</v>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
       </c>
       <c r="H11">
+        <v>127999</v>
+      </c>
+      <c r="I11" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J11">
         <v>779</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>776</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>3</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
         <v>2</v>
       </c>
-      <c r="N11" s="3">
+      <c r="P11" s="3">
         <v>6.8750537113571193</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
       <c r="D12" t="s">
         <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12">
-        <v>127999</v>
-      </c>
-      <c r="G12" s="2">
-        <v>639.995</v>
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
       </c>
       <c r="H12">
+        <v>127999</v>
+      </c>
+      <c r="I12" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J12">
         <v>800</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>797</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>3</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
       <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3">
         <v>0.15625122071266179</v>
       </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
       <c r="D13" t="s">
         <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>62</v>
       </c>
-      <c r="F13">
-        <v>127999</v>
-      </c>
-      <c r="G13" s="2">
-        <v>639.995</v>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
       </c>
       <c r="H13">
+        <v>127999</v>
+      </c>
+      <c r="I13" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J13">
         <v>749</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>748</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
         <v>3</v>
       </c>
-      <c r="N13" s="3">
+      <c r="P13" s="3">
         <v>1.250009765701295</v>
       </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
       <c r="D14" t="s">
         <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>66</v>
       </c>
-      <c r="F14">
-        <v>127999</v>
-      </c>
-      <c r="G14" s="2">
-        <v>639.995</v>
+      <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" t="s">
+        <v>68</v>
       </c>
       <c r="H14">
+        <v>127999</v>
+      </c>
+      <c r="I14" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J14">
         <v>604</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>600</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>4</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14" s="3">
         <v>0.93750732427597094</v>
       </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
       <c r="D15" t="s">
         <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15">
-        <v>127999</v>
-      </c>
-      <c r="G15" s="2">
-        <v>639.995</v>
+        <v>70</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" t="s">
+        <v>68</v>
       </c>
       <c r="H15">
+        <v>127999</v>
+      </c>
+      <c r="I15" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J15">
         <v>714</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>713</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>6</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>7.1875561527824443</v>
       </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
       <c r="D16" t="s">
         <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>73</v>
       </c>
-      <c r="F16">
-        <v>127999</v>
-      </c>
-      <c r="G16" s="2">
-        <v>639.995</v>
+      <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s">
+        <v>75</v>
       </c>
       <c r="H16">
+        <v>127999</v>
+      </c>
+      <c r="I16" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J16">
         <v>716</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>584</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>132</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>3</v>
       </c>
-      <c r="N16" s="3">
+      <c r="P16" s="3">
         <v>2.2656427003335962</v>
       </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0</v>
+      </c>
+      <c r="S16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
       <c r="D17" t="s">
         <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17">
-        <v>127999</v>
-      </c>
-      <c r="G17" s="2">
-        <v>639.995</v>
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" t="s">
+        <v>75</v>
       </c>
       <c r="H17">
+        <v>127999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J17">
         <v>726</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>597</v>
       </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>129</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17" s="3">
         <v>1.562512207126618</v>
       </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
       <c r="D18" t="s">
         <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>80</v>
       </c>
-      <c r="F18">
-        <v>127999</v>
-      </c>
-      <c r="G18" s="2">
-        <v>639.995</v>
+      <c r="F18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" t="s">
+        <v>82</v>
       </c>
       <c r="H18">
+        <v>127999</v>
+      </c>
+      <c r="I18" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J18">
         <v>558</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>493</v>
       </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>65</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>4</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1.640637817482949</v>
       </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>82</v>
-      </c>
       <c r="D19" t="s">
         <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19">
-        <v>127999</v>
-      </c>
-      <c r="G19" s="2">
-        <v>639.995</v>
+        <v>84</v>
+      </c>
+      <c r="F19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" t="s">
+        <v>82</v>
       </c>
       <c r="H19">
+        <v>127999</v>
+      </c>
+      <c r="I19" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J19">
         <v>603</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>578</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>25</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19" s="3">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3">
         <v>0.15625122071266179</v>
       </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
       <c r="D20" t="s">
         <v>86</v>
       </c>
       <c r="E20" t="s">
         <v>87</v>
       </c>
-      <c r="F20">
-        <v>127999</v>
-      </c>
-      <c r="G20" s="2">
-        <v>639.995</v>
+      <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" t="s">
+        <v>89</v>
       </c>
       <c r="H20">
+        <v>127999</v>
+      </c>
+      <c r="I20" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J20">
         <v>518</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>518</v>
       </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3">
         <v>0.15625122071266179</v>
       </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
       <c r="D21" t="s">
         <v>90</v>
       </c>
       <c r="E21" t="s">
         <v>91</v>
       </c>
-      <c r="F21">
-        <v>127999</v>
-      </c>
-      <c r="G21" s="2">
-        <v>639.995</v>
+      <c r="F21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" t="s">
+        <v>93</v>
       </c>
       <c r="H21">
+        <v>127999</v>
+      </c>
+      <c r="I21" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J21">
         <v>620</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>619</v>
       </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
         <v>2</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2.109391479620935</v>
       </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>93</v>
-      </c>
       <c r="D22" t="s">
         <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22">
-        <v>127999</v>
-      </c>
-      <c r="G22" s="2">
-        <v>639.995</v>
+        <v>95</v>
+      </c>
+      <c r="F22" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" t="s">
+        <v>93</v>
       </c>
       <c r="H22">
+        <v>127999</v>
+      </c>
+      <c r="I22" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J22">
         <v>613</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>612</v>
       </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3">
         <v>0.15625122071266179</v>
       </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
       <c r="D23" t="s">
         <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>98</v>
       </c>
-      <c r="F23">
-        <v>127999</v>
-      </c>
-      <c r="G23" s="2">
-        <v>639.995</v>
+      <c r="F23" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" t="s">
+        <v>100</v>
       </c>
       <c r="H23">
+        <v>127999</v>
+      </c>
+      <c r="I23" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J23">
         <v>998</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>875</v>
       </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>123</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>5</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1.562512207126618</v>
       </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
       </c>
       <c r="D24" t="s">
         <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
-      </c>
-      <c r="F24">
-        <v>127999</v>
-      </c>
-      <c r="G24" s="2">
-        <v>639.995</v>
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
+        <v>100</v>
       </c>
       <c r="H24">
+        <v>127999</v>
+      </c>
+      <c r="I24" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J24">
         <v>777</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>672</v>
       </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>105</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>0.54687927249431634</v>
       </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
       <c r="D25" t="s">
         <v>104</v>
       </c>
       <c r="E25" t="s">
         <v>105</v>
       </c>
-      <c r="F25">
-        <v>127999</v>
-      </c>
-      <c r="G25" s="2">
-        <v>639.995</v>
+      <c r="F25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" t="s">
+        <v>107</v>
       </c>
       <c r="H25">
+        <v>127999</v>
+      </c>
+      <c r="I25" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J25">
         <v>846</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>846</v>
       </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25" s="3">
         <v>0.31250244142532357</v>
       </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
       <c r="D26" t="s">
         <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>109</v>
       </c>
-      <c r="F26">
-        <v>127999</v>
-      </c>
-      <c r="G26" s="2">
-        <v>639.995</v>
+      <c r="F26" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" t="s">
+        <v>111</v>
       </c>
       <c r="H26">
+        <v>127999</v>
+      </c>
+      <c r="I26" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J26">
         <v>548</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>547</v>
       </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26" s="3">
         <v>0.93750732427597094</v>
       </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
       <c r="D27" t="s">
         <v>112</v>
       </c>
       <c r="E27" t="s">
         <v>113</v>
       </c>
-      <c r="F27">
-        <v>127999</v>
-      </c>
-      <c r="G27" s="2">
-        <v>639.995</v>
+      <c r="F27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" t="s">
+        <v>115</v>
       </c>
       <c r="H27">
+        <v>127999</v>
+      </c>
+      <c r="I27" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J27">
         <v>880</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>869</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>11</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
       <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
         <v>7</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3.5937780763912222</v>
       </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
       <c r="D28" t="s">
         <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>117</v>
       </c>
-      <c r="F28">
-        <v>127999</v>
-      </c>
-      <c r="G28" s="2">
-        <v>639.995</v>
+      <c r="F28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" t="s">
+        <v>119</v>
       </c>
       <c r="H28">
+        <v>127999</v>
+      </c>
+      <c r="I28" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J28">
         <v>745</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>724</v>
       </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>21</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>5</v>
       </c>
-      <c r="N28" s="3">
+      <c r="P28" s="3">
         <v>1.7968890381956111</v>
       </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
       <c r="D29" t="s">
         <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29">
-        <v>127999</v>
-      </c>
-      <c r="G29" s="2">
-        <v>639.995</v>
+        <v>121</v>
+      </c>
+      <c r="F29" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" t="s">
+        <v>119</v>
       </c>
       <c r="H29">
+        <v>127999</v>
+      </c>
+      <c r="I29" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J29">
         <v>851</v>
       </c>
-      <c r="I29">
+      <c r="K29">
         <v>841</v>
       </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>10</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
         <v>11</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>15.078242798771869</v>
       </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" t="s">
-        <v>122</v>
-      </c>
       <c r="D30" t="s">
         <v>123</v>
       </c>
       <c r="E30" t="s">
         <v>124</v>
       </c>
-      <c r="F30">
-        <v>127999</v>
-      </c>
-      <c r="G30" s="2">
-        <v>639.995</v>
+      <c r="F30" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" t="s">
+        <v>126</v>
       </c>
       <c r="H30">
+        <v>127999</v>
+      </c>
+      <c r="I30" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J30">
         <v>759</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>758</v>
       </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
         <v>8</v>
       </c>
-      <c r="N30" s="3">
+      <c r="P30" s="3">
         <v>4.0625317385292066</v>
       </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" t="s">
-        <v>126</v>
-      </c>
       <c r="D31" t="s">
         <v>127</v>
       </c>
       <c r="E31" t="s">
         <v>128</v>
       </c>
-      <c r="F31">
-        <v>127999</v>
-      </c>
-      <c r="G31" s="2">
-        <v>639.995</v>
+      <c r="F31" t="s">
+        <v>129</v>
+      </c>
+      <c r="G31" t="s">
+        <v>130</v>
       </c>
       <c r="H31">
+        <v>127999</v>
+      </c>
+      <c r="I31" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J31">
         <v>655</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>654</v>
       </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
         <v>2</v>
       </c>
-      <c r="N31" s="3">
+      <c r="P31" s="3">
         <v>0.62500488285064726</v>
       </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>129</v>
-      </c>
-      <c r="C32" t="s">
-        <v>130</v>
-      </c>
       <c r="D32" t="s">
         <v>131</v>
       </c>
       <c r="E32" t="s">
         <v>132</v>
       </c>
-      <c r="F32">
-        <v>127999</v>
-      </c>
-      <c r="G32" s="2">
-        <v>639.995</v>
+      <c r="F32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G32" t="s">
+        <v>134</v>
       </c>
       <c r="H32">
+        <v>127999</v>
+      </c>
+      <c r="I32" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J32">
         <v>652</v>
       </c>
-      <c r="I32">
+      <c r="K32">
         <v>651</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>3.5156524660348909</v>
       </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" t="s">
-        <v>134</v>
-      </c>
       <c r="D33" t="s">
         <v>135</v>
       </c>
       <c r="E33" t="s">
         <v>136</v>
       </c>
-      <c r="F33">
-        <v>127999</v>
-      </c>
-      <c r="G33" s="2">
-        <v>639.995</v>
+      <c r="F33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G33" t="s">
+        <v>138</v>
       </c>
       <c r="H33">
+        <v>127999</v>
+      </c>
+      <c r="I33" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J33">
         <v>560</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>508</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>52</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
         <v>2</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2.109391479620935</v>
       </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>137</v>
-      </c>
-      <c r="C34" t="s">
-        <v>138</v>
-      </c>
       <c r="D34" t="s">
         <v>139</v>
       </c>
       <c r="E34" t="s">
-        <v>136</v>
-      </c>
-      <c r="F34">
-        <v>127999</v>
-      </c>
-      <c r="G34" s="2">
-        <v>639.995</v>
+        <v>140</v>
+      </c>
+      <c r="F34" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" t="s">
+        <v>138</v>
       </c>
       <c r="H34">
+        <v>127999</v>
+      </c>
+      <c r="I34" s="2">
+        <v>639.995</v>
+      </c>
+      <c r="J34">
         <v>651</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>626</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>25</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
       <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34" s="3">
         <v>0.15625122071266179</v>
       </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" t="s">
-        <v>141</v>
-      </c>
       <c r="D35" t="s">
         <v>142</v>
       </c>
       <c r="E35" t="s">
         <v>143</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="s">
+        <v>144</v>
+      </c>
+      <c r="G35" t="s">
+        <v>145</v>
+      </c>
+      <c r="H35">
         <v>128000</v>
       </c>
-      <c r="G35" s="2">
+      <c r="I35" s="2">
         <v>640</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>714</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>613</v>
       </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>101</v>
       </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35" s="3">
         <v>0.78125</v>
       </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>144</v>
-      </c>
-      <c r="C36" t="s">
-        <v>145</v>
-      </c>
       <c r="D36" t="s">
         <v>146</v>
       </c>
       <c r="E36" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36">
+        <v>147</v>
+      </c>
+      <c r="F36" t="s">
+        <v>148</v>
+      </c>
+      <c r="G36" t="s">
+        <v>145</v>
+      </c>
+      <c r="H36">
         <v>128000</v>
       </c>
-      <c r="G36" s="2">
+      <c r="I36" s="2">
         <v>640</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>718</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>608</v>
       </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>110</v>
       </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" s="3">
+      <c r="N36">
         <v>0</v>
       </c>
       <c r="O36">
@@ -2755,8 +2763,14 @@
       <c r="P36" s="3">
         <v>0</v>
       </c>
-      <c r="Q36" t="s">
-        <v>21</v>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36" s="3">
+        <v>0</v>
+      </c>
+      <c r="S36" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
